--- a/AAII_Financials/Quarterly/AGESY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AGESY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="92">
   <si>
     <t>AGESY</t>
   </si>
@@ -656,90 +656,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -782,23 +788,29 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3">
         <v>6932700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>5858300</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3">
         <v>5819000</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -856,8 +868,14 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -915,8 +933,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -938,8 +962,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -997,8 +1023,14 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1056,8 +1088,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1100,23 +1138,29 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>31300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>44600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>138600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1159,11 +1203,11 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1174,8 +1218,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1194,8 +1244,10 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1238,23 +1290,29 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3">
         <v>6419400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>6677700</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3">
         <v>4639300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1297,23 +1355,29 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>513300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-819300</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>1179700</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1335,8 +1399,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1379,23 +1445,29 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
         <v>188000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1482000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
         <v>-81500</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1453,8 +1525,14 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1497,23 +1575,29 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3">
         <v>63800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>63100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3">
         <v>59200</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1556,23 +1640,29 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3">
         <v>637600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>599500</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3">
         <v>1039000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1615,23 +1705,29 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3">
         <v>126400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>116400</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3">
         <v>133300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1689,8 +1785,14 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1733,23 +1835,29 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3">
         <v>511200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>483100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3">
         <v>905600</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1792,23 +1900,29 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3">
         <v>439800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>380800</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3">
         <v>836900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1866,8 +1980,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1910,11 +2030,11 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -1925,8 +2045,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1984,8 +2110,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2043,8 +2175,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2087,23 +2225,29 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
         <v>-188000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1482000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
         <v>81500</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2146,23 +2290,29 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3">
         <v>439800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>380800</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3">
         <v>836900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2220,8 +2370,14 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2264,87 +2420,99 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3">
         <v>439800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>380800</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3">
         <v>836900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2366,8 +2534,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2389,115 +2559,123 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2723600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2748800</v>
+      </c>
+      <c r="F41" s="3">
         <v>3642100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3639600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4184400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3851100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2149300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2315400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2395800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2412300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2072500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1984500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1651700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1643900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1232200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>28562800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>28826200</v>
+      </c>
+      <c r="F42" s="3">
         <v>28059200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>28039400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>26933600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>24788200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>23845100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>25688200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>22979700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>23138400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>24283200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>23252500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>21946500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>21841600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>639100</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
@@ -2507,67 +2685,79 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1390200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1389200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>12900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>11900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1202000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1294900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>20400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>20500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1112000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1064800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>22900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>22800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1273600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2610,11 +2800,11 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -2625,56 +2815,62 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5278200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5326900</v>
+      </c>
+      <c r="F45" s="3">
         <v>3419000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3416600</v>
       </c>
-      <c r="F45" s="3">
-        <v>1017000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>936000</v>
-      </c>
       <c r="H45" s="3">
+        <v>4103300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3776500</v>
+      </c>
+      <c r="J45" s="3">
         <v>1921500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2070000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3324800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3347700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2188600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2095700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>5485800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>5459600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>6811300</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
@@ -2684,115 +2880,127 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36574900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>36912300</v>
+      </c>
+      <c r="F46" s="3">
         <v>36510500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>36484800</v>
       </c>
-      <c r="F46" s="3">
-        <v>32148000</v>
-      </c>
-      <c r="G46" s="3">
-        <v>29587100</v>
-      </c>
       <c r="H46" s="3">
+        <v>35234300</v>
+      </c>
+      <c r="I46" s="3">
+        <v>32427600</v>
+      </c>
+      <c r="J46" s="3">
         <v>29117900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>31368500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>28720700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>28919000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>29656200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>28397500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>29107000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>28967800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>9956200</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
+      <c r="S46" s="3">
+        <v>0</v>
       </c>
       <c r="T46" s="3">
         <v>0</v>
       </c>
-      <c r="U46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>68097800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>68725900</v>
+      </c>
+      <c r="F47" s="3">
         <v>68550000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>68501700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>64340600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>59215300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>57070100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>61481200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>57562400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>57959900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>59931500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>57387800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>56378800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>56109300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>54838100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2802,126 +3010,144 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3548500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3581200</v>
+      </c>
+      <c r="F48" s="3">
         <v>3521200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3518700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3059300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2815600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2670000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2876400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2616500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2634600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2665000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2551900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2449800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2438100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2380000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4991400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5037500</v>
+      </c>
+      <c r="F49" s="3">
         <v>5154400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5150800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1967100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1810400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1683400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1813500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1686500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1698100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1635900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1566500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1579700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1572100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2064800</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2979,8 +3205,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3038,67 +3270,79 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3210300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3239900</v>
+      </c>
+      <c r="F52" s="3">
         <v>3504800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3502300</v>
       </c>
-      <c r="F52" s="3">
-        <v>6566100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>6043000</v>
-      </c>
       <c r="H52" s="3">
+        <v>3479700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3202600</v>
+      </c>
+      <c r="J52" s="3">
         <v>3153500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3397300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3242300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3264600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3370200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3227100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>6000000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>5971300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>20258600</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3156,67 +3400,79 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>125485000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>126642500</v>
+      </c>
+      <c r="F54" s="3">
         <v>125716800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>125628300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>116826800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>107520500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>101930800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>109809300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>103708300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>104424400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>106878500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>102342300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>108064400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>107547800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>107196800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T54" s="3">
-        <v>0</v>
-      </c>
-      <c r="U54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3">
+        <v>0</v>
+      </c>
+      <c r="W54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3238,8 +3494,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3261,56 +3519,58 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F57" s="3">
         <v>407400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>407100</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>320900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>345800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>99600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>100300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>260900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>249800</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3">
         <v>7326100</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
@@ -3320,233 +3580,257 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2515700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2538900</v>
+      </c>
+      <c r="F58" s="3">
         <v>3092600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3090500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2769200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2548600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2500300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2693500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2743000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2761900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3191100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3055700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3164800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3149700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2716700</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>725600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>725100</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>542500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>584400</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>548200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>525000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>4419200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4398100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6273400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6071100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6127100</v>
+      </c>
+      <c r="F60" s="3">
         <v>5021700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5018200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5843800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5378300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3942400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4247200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5550200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5588500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4582700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4388200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7584100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7547800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>17285500</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="S60" s="3">
+        <v>0</v>
       </c>
       <c r="T60" s="3">
         <v>0</v>
       </c>
-      <c r="U60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7780200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7852000</v>
+      </c>
+      <c r="F61" s="3">
         <v>7389900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7384700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5701700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5247500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4083200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4398800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4509800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4540900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4286500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4104600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4527300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4505600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4048300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3556,67 +3840,79 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>97855600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>98758200</v>
+      </c>
+      <c r="F62" s="3">
         <v>98260000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>98190800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>94090400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>86595300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>83604900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>90066900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>84063000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>84643400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>87332800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>83626200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>86541500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>86127800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>75482500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3674,8 +3970,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3733,8 +4035,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3792,67 +4100,79 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>112342100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>113378300</v>
+      </c>
+      <c r="F66" s="3">
         <v>112210900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>112131900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>106094000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>97642700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>92823300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>99997800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>94555900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>95208800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>97484200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>93346700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>99108100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>98634300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>97971600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T66" s="3">
-        <v>0</v>
-      </c>
-      <c r="U66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3">
+        <v>0</v>
+      </c>
+      <c r="W66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3874,8 +4194,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3933,8 +4255,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3992,8 +4320,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4051,8 +4385,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4110,67 +4450,79 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>46100</v>
+      </c>
+      <c r="F72" s="3">
         <v>2058200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2056800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>819700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>754400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1164700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1254700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>707200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>712100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1060000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1015000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>625500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>622600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1080500</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4228,8 +4580,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4287,8 +4645,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4346,56 +4710,62 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11679400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>11787200</v>
+      </c>
+      <c r="F76" s="3">
         <v>11084900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11077100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9485600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8730000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8025700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8646000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8077800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>8133600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>8203800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7855600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>7887600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7849800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>8103000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4405,8 +4775,14 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4464,72 +4840,84 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4572,23 +4960,29 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3">
         <v>439800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>380800</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3">
         <v>836900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4610,41 +5004,43 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>102200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>94000</v>
+      </c>
+      <c r="F83" s="3">
         <v>61100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>65800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>84100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>84700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>-90100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>-86300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>105900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>105400</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4660,17 +5056,23 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4728,8 +5130,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4787,8 +5195,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4846,8 +5260,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4905,8 +5325,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4964,67 +5390,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1035600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1045200</v>
+      </c>
+      <c r="F89" s="3">
         <v>959300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>958600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>742200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>683100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>291400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>314000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>258200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>260000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>138700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>132800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-71000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-70600</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5046,55 +5484,57 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-93100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-60500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-60400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-49300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-45400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-85900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-92600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-41300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-41500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-53100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-50800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-27300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-27200</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -5105,8 +5545,14 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5164,8 +5610,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5223,67 +5675,79 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-683200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-689500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1502300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1501200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-74600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-68600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-147500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-158900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>202500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>203900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>245400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>235000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>496200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>493800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5305,55 +5769,57 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>264500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>266900</v>
+      </c>
+      <c r="F96" s="3">
         <v>176100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>176000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>209600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>192900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>139200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>150000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>168800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>169900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>149200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>142900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>147400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>146700</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
+      <c r="R96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -5364,8 +5830,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5423,8 +5895,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5482,8 +5960,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5541,100 +6025,112 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-764900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-771900</v>
+      </c>
+      <c r="F100" s="3">
         <v>280000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>279800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>226700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>208600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-230900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-248700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-271100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-273000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-217200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-208000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-257600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-256400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="F101" s="3">
         <v>4100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>4500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>3800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>3800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-3300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-3200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>3800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>3800</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5650,72 +6146,84 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-410100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-413900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-270600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-270400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>873200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>803600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-82800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-89200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>193400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>194700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>163600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>156600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>171400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>170600</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>
